--- a/healthcare_forms/008_healthcare_design_thinking_lab_filming_consent_form--healthcare_forms.xlsx
+++ b/healthcare_forms/008_healthcare_design_thinking_lab_filming_consent_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'recording_for_education_and_research_purposes'}</t>
+          <t>recording_for_education_and_research_purposes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Recording for education and research purposes'}</t>
+          <t>Recording for education and research purposes</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'recording_for_promotional_use_by_our_organization'}</t>
+          <t>recording_for_promotional_use_by_our_organization</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Recording for promotional use by our organization'}</t>
+          <t>Recording for promotional use by our organization</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'recording_for_internal_project_team_meetings'}</t>
+          <t>recording_for_internal_project_team_meetings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Recording for internal project team meetings'}</t>
+          <t>Recording for internal project team meetings</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'video'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Video'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'audio'}</t>
+          <t>audio</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Audio'}</t>
+          <t>Audio</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'phone_number'}</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Phone Number'}</t>
+          <t>Phone Number</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'participant'}</t>
+          <t>participant</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Participant'}</t>
+          <t>Participant</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'representative'}</t>
+          <t>representative</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Representative'}</t>
+          <t>Representative</t>
         </is>
       </c>
     </row>
